--- a/public/Excel/ProjectsList.xlsx
+++ b/public/Excel/ProjectsList.xlsx
@@ -14,150 +14,447 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="147">
+  <si>
+    <t>S.No</t>
+  </si>
   <si>
     <t>Project Title</t>
   </si>
   <si>
+    <t>Dept</t>
+  </si>
+  <si>
     <t>Domain</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Deep Learning for Image Classification</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
-  </si>
-  <si>
-    <t>A CNN-based system for classifying images into multiple categories.</t>
+    <t>Rain Water Harvesting</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>A environmental based project titled 'Rain Water Harvesting' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Smart Energy Meter</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>Power Systems</t>
+  </si>
+  <si>
+    <t>A power systems based project titled 'Smart Energy Meter' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Solar EV Charger</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>A renewable energy based project titled 'Solar EV Charger' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>E-commerce Website</t>
+  </si>
+  <si>
+    <t>CSE</t>
+  </si>
+  <si>
+    <t>Web Development</t>
+  </si>
+  <si>
+    <t>A web development based project titled 'E-commerce Website' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>DTMF based Home Control</t>
+  </si>
+  <si>
+    <t>ECE</t>
+  </si>
+  <si>
+    <t>Communication Systems</t>
+  </si>
+  <si>
+    <t>A communication systems based project titled 'DTMF based Home Control' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Hexapod Robot</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>A robotics based project titled 'Hexapod Robot' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Crypto Wallet</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>A blockchain based project titled 'Crypto Wallet' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Heat Exchanger CFD</t>
+  </si>
+  <si>
+    <t>Thermal</t>
+  </si>
+  <si>
+    <t>A thermal based project titled 'Heat Exchanger CFD' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Hotel Booking System</t>
+  </si>
+  <si>
+    <t>Java Projects</t>
+  </si>
+  <si>
+    <t>A java projects based project titled 'Hotel Booking System' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Face Recognition System</t>
+  </si>
+  <si>
+    <t>AI / ML</t>
+  </si>
+  <si>
+    <t>A ai / ml based project titled 'Face Recognition System' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Smart Traffic System</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>A iot based project titled 'Smart Traffic System' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Air Quality Monitoring</t>
+  </si>
+  <si>
+    <t>A environmental based project titled 'Air Quality Monitoring' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Hybrid Vehicle Design</t>
+  </si>
+  <si>
+    <t>Automobile</t>
+  </si>
+  <si>
+    <t>A automobile based project titled 'Hybrid Vehicle Design' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Structural Health Monitoring</t>
+  </si>
+  <si>
+    <t>Smart Cities</t>
+  </si>
+  <si>
+    <t>A smart cities based project titled 'Structural Health Monitoring' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Noise Filter using MATLAB</t>
+  </si>
+  <si>
+    <t>Signal Processing</t>
+  </si>
+  <si>
+    <t>A signal processing based project titled 'Noise Filter using MATLAB' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Smart Helmet</t>
+  </si>
+  <si>
+    <t>Embedded Systems</t>
+  </si>
+  <si>
+    <t>A embedded systems based project titled 'Smart Helmet' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Loan Approval Prediction</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>A data science based project titled 'Loan Approval Prediction' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>File Organizer Script</t>
+  </si>
+  <si>
+    <t>Python Projects</t>
+  </si>
+  <si>
+    <t>A python projects based project titled 'File Organizer Script' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>EV Charging Station</t>
+  </si>
+  <si>
+    <t>Electric Vehicles</t>
+  </si>
+  <si>
+    <t>A electric vehicles based project titled 'EV Charging Station' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Plastic Waste Road</t>
+  </si>
+  <si>
+    <t>A environmental based project titled 'Plastic Waste Road' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>College Enquiry Chatbot</t>
+  </si>
+  <si>
+    <t>A web development based project titled 'College Enquiry Chatbot' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Solar Powered Irrigation</t>
+  </si>
+  <si>
+    <t>A renewable energy based project titled 'Solar Powered Irrigation' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Line Follower Robot</t>
+  </si>
+  <si>
+    <t>A embedded systems based project titled 'Line Follower Robot' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Pick and Place Robot</t>
+  </si>
+  <si>
+    <t>A robotics based project titled 'Pick and Place Robot' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Health Tracker App</t>
+  </si>
+  <si>
+    <t>App Development</t>
+  </si>
+  <si>
+    <t>A app development based project titled 'Health Tracker App' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Battery Management System</t>
+  </si>
+  <si>
+    <t>A electric vehicles based project titled 'Battery Management System' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Urban Planning Tool</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>A gis based project titled 'Urban Planning Tool' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Audio Signal Analysis</t>
+  </si>
+  <si>
+    <t>A signal processing based project titled 'Audio Signal Analysis' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>IoT Solar Tracker</t>
+  </si>
+  <si>
+    <t>IoT for Energy</t>
+  </si>
+  <si>
+    <t>A iot for energy based project titled 'IoT Solar Tracker' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Weather App using API</t>
+  </si>
+  <si>
+    <t>A python projects based project titled 'Weather App using API' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Green Building Design</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>A construction based project titled 'Green Building Design' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Voice Controlled Devices</t>
+  </si>
+  <si>
+    <t>A signal processing based project titled 'Voice Controlled Devices' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Low Cost Housing Model</t>
+  </si>
+  <si>
+    <t>A construction based project titled 'Low Cost Housing Model' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Automatic Braking System</t>
+  </si>
+  <si>
+    <t>A automobile based project titled 'Automatic Braking System' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>3D Printed Drone Frame</t>
+  </si>
+  <si>
+    <t>3D Printing</t>
+  </si>
+  <si>
+    <t>A 3d printing based project titled '3D Printed Drone Frame' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>IoT-based Home Automation</t>
+  </si>
+  <si>
+    <t>A iot based project titled 'IoT-based Home Automation' suitable for ECE students.</t>
+  </si>
+  <si>
+    <t>Thermal Analysis of Engine</t>
+  </si>
+  <si>
+    <t>A thermal based project titled 'Thermal Analysis of Engine' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Automated Forklift</t>
+  </si>
+  <si>
+    <t>A robotics based project titled 'Automated Forklift' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Smart Street Lighting</t>
+  </si>
+  <si>
+    <t>A smart cities based project titled 'Smart Street Lighting' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>PDF Merger Tool</t>
+  </si>
+  <si>
+    <t>A python projects based project titled 'PDF Merger Tool' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>College Event App</t>
+  </si>
+  <si>
+    <t>A app development based project titled 'College Event App' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Bridge Load Simulation</t>
+  </si>
+  <si>
+    <t>A construction based project titled 'Bridge Load Simulation' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>3D Printed Robotic Arm</t>
+  </si>
+  <si>
+    <t>A 3d printing based project titled '3D Printed Robotic Arm' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Hybrid Energy System</t>
+  </si>
+  <si>
+    <t>A renewable energy based project titled 'Hybrid Energy System' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Wireless EV Charging</t>
+  </si>
+  <si>
+    <t>A electric vehicles based project titled 'Wireless EV Charging' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Waste Collection System</t>
+  </si>
+  <si>
+    <t>A smart cities based project titled 'Waste Collection System' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>Customer Segmentation</t>
+  </si>
+  <si>
+    <t>A data science based project titled 'Customer Segmentation' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Energy Monitoring System</t>
+  </si>
+  <si>
+    <t>A iot for energy based project titled 'Energy Monitoring System' suitable for EEE students.</t>
   </si>
   <si>
     <t>Stock Price Prediction</t>
   </si>
   <si>
-    <t>Machine Learning</t>
-  </si>
-  <si>
-    <t>Predicting stock prices using regression and time series analysis.</t>
-  </si>
-  <si>
-    <t>Big Data Analytics Platform</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>A scalable platform for processing and visualizing large datasets.</t>
-  </si>
-  <si>
-    <t>Customer Churn Analysis</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>Data-driven insights to predict and reduce customer churn.</t>
-  </si>
-  <si>
-    <t>Smart Home Automation</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>IoT-based system to automate and monitor home appliances.</t>
-  </si>
-  <si>
-    <t>E-commerce Website</t>
-  </si>
-  <si>
-    <t>Web Dev</t>
-  </si>
-  <si>
-    <t>A full-stack e-commerce platform with payment integration.</t>
-  </si>
-  <si>
-    <t>Personal Portfolio</t>
-  </si>
-  <si>
-    <t>Front End</t>
-  </si>
-  <si>
-    <t>A responsive personal portfolio website using React.js.</t>
-  </si>
-  <si>
-    <t>Library Management System</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>A desktop application for managing library books and members.</t>
-  </si>
-  <si>
-    <t>Student Management Portal</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>A web-based portal for managing student records and grades.</t>
-  </si>
-  <si>
-    <t>Handwriting Recognition</t>
-  </si>
-  <si>
-    <t>Pattern Recognition</t>
-  </si>
-  <si>
-    <t>A neural network to recognize handwritten digits and characters.</t>
-  </si>
-  <si>
-    <t>Campus Navigation App</t>
-  </si>
-  <si>
-    <t>Android Dev</t>
-  </si>
-  <si>
-    <t>An Android app to help students navigate the campus easily.</t>
-  </si>
-  <si>
-    <t>Network Intrusion Detection</t>
-  </si>
-  <si>
-    <t>Cyber Security</t>
-  </si>
-  <si>
-    <t>A system to detect and prevent network intrusions using ML.</t>
-  </si>
-  <si>
-    <t>Bug Tracking System</t>
-  </si>
-  <si>
-    <t>Software Engineering</t>
-  </si>
-  <si>
-    <t>A collaborative tool for tracking and managing software bugs.</t>
-  </si>
-  <si>
-    <t>Social Media Data Mining</t>
-  </si>
-  <si>
-    <t>Data Mining</t>
-  </si>
-  <si>
-    <t>Mining and analyzing trends from social media data streams.</t>
-  </si>
-  <si>
-    <t>AI Chatbot</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>A conversational AI chatbot for customer support.</t>
+    <t>A ai / ml based project titled 'Stock Price Prediction' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Blockchain Voting</t>
+  </si>
+  <si>
+    <t>A blockchain based project titled 'Blockchain Voting' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Flood Risk Mapping</t>
+  </si>
+  <si>
+    <t>A gis based project titled 'Flood Risk Mapping' suitable for Civil students.</t>
+  </si>
+  <si>
+    <t>IoT Smart Grid</t>
+  </si>
+  <si>
+    <t>A iot for energy based project titled 'IoT Smart Grid' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Load Balancing System</t>
+  </si>
+  <si>
+    <t>A power systems based project titled 'Load Balancing System' suitable for EEE students.</t>
+  </si>
+  <si>
+    <t>Solar Water Heater</t>
+  </si>
+  <si>
+    <t>A thermal based project titled 'Solar Water Heater' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Fake News Detection</t>
+  </si>
+  <si>
+    <t>A ai / ml based project titled 'Fake News Detection' suitable for CSE students.</t>
+  </si>
+  <si>
+    <t>Smart Vehicle Tracking</t>
+  </si>
+  <si>
+    <t>A automobile based project titled 'Smart Vehicle Tracking' suitable for Mechanical students.</t>
+  </si>
+  <si>
+    <t>Gesture Controlled Robot</t>
+  </si>
+  <si>
+    <t>A embedded systems based project titled 'Gesture Controlled Robot' suitable for ECE students.</t>
   </si>
 </sst>
 </file>
@@ -165,7 +462,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,61 +472,27 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF374151"/>
-      <name val="Ui-sans-serif"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF374151"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1f2937"/>
-      <name val="Ui-sans-serif"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF374151"/>
-      <name val="Ui-sans-serif"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4b5563"/>
-      <name val="Ui-sans-serif"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFf3f4f6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFf9fafb"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -239,48 +502,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -310,28 +571,28 @@
         <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -587,188 +848,2071 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="56.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="33.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
-      <c r="A3" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
-      <c r="A4" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
-      <c r="A5" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
-      <c r="A6" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
-      <c r="A7" s="3" t="s">
+      <c r="B17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
-      <c r="A8" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
-      <c r="A9" s="3" t="s">
+      <c r="B24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="B26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
-      <c r="A10" s="3" t="s">
+      <c r="B27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
-      <c r="A11" s="3" t="s">
+      <c r="B30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="B32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
-      <c r="A12" s="3" t="s">
+      <c r="B33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="B35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
-      <c r="A13" s="3" t="s">
+      <c r="B36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="B38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
-      <c r="A14" s="3" t="s">
+      <c r="B39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="B41" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
-      <c r="A15" s="3" t="s">
+      <c r="B42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B43" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="B44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
-      <c r="A16" s="6" t="s">
+      <c r="B45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="B47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+      <c r="A48" s="3">
         <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
